--- a/nonprofit_employee_forms/004_volunteer_interest_form--nonprofit_employee_forms.xlsx
+++ b/nonprofit_employee_forms/004_volunteer_interest_form--nonprofit_employee_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_1</t>
+          <t>volunteer_interest_form_1_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Volunteer Role</t>
+          <t>Volunteer Interest Form 1 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -612,7 +612,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_2</t>
+          <t>volunteer_interest_form_2_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Volunteer Availability</t>
+          <t>Volunteer Interest Form 4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -681,7 +681,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_4</t>
+          <t>volunteer_interest_form_4_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Volunteer Availability</t>
+          <t>Volunteer Interest Form 8</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_8</t>
+          <t>volunteer_interest_form_8_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Volunteer Interest Form 8 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Contact Information</t>
+          <t>Volunteer Interest Form 10</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,7 +865,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_9</t>
+          <t>volunteer_interest_form_9_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_10</t>
+          <t>volunteer_interest_form_10_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_1_choices</t>
+          <t>volunteer_interest_form_1_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_1_choices</t>
+          <t>volunteer_interest_form_1_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1187,14 +1187,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>volunteer_admin</t>
+          <t>volunteer admin</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_1_choices</t>
+          <t>volunteer_interest_form_1_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>volunteer_ambassador</t>
+          <t>volunteer ambassador</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_4_choices</t>
+          <t>volunteer_interest_form_4_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_4_choices</t>
+          <t>volunteer_interest_form_4_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_4_choices</t>
+          <t>volunteer_interest_form_4_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>volunteer_interest_form_4_choices</t>
+          <t>volunteer_interest_form_4_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
